--- a/artfynd/A 41375-2024 artfynd.xlsx
+++ b/artfynd/A 41375-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104657373</v>
+        <v>104657380</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580265.5599712223</v>
+        <v>578156</v>
       </c>
       <c r="R2" t="n">
-        <v>7370705.742390305</v>
+        <v>7370859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,6 +780,328 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104657375</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>S Lillviken-Jutis, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>580431</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7370634</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104657373</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>S Lillviken-Jutis, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>580266</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7370706</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-07-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Engla Grönvall, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5995485</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99121</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223614</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig brudsporre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ringselet, korsning Silvervägen/väg mot Tjärnberg, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>579965</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7370817</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2011-08-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2011-08-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>rikt vägdike</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Charlotte Nordgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 41375-2024 artfynd.xlsx
+++ b/artfynd/A 41375-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657375</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657380</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104657373</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,8 +1124,19 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5995485</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>